--- a/cp-date/ig/all-profiles.xlsx
+++ b/cp-date/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T12:13:06+00:00</t>
+    <t>2026-05-05T12:29:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="F28" s="2"/>
       <c r="G28" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>84</v>

--- a/cp-date/ig/all-profiles.xlsx
+++ b/cp-date/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T12:29:58+00:00</t>
+    <t>2026-05-06T12:23:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -73532,7 +73532,7 @@
       </c>
       <c r="F649" s="2"/>
       <c r="G649" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H649" t="s" s="2">
         <v>84</v>
